--- a/data/availability/projects/palm-hills-developments/palm-hills-alexandria.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-alexandria.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for palm-hills-alexandria</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -959,7 +969,6 @@
       <c r="G2" t="n">
         <v>194.3</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1016,7 +1025,6 @@
       <c r="G3" t="n">
         <v>194.3</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1073,7 +1081,6 @@
       <c r="G4" t="n">
         <v>194.3</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1130,7 +1137,6 @@
       <c r="G5" t="n">
         <v>194.3</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1187,7 +1193,6 @@
       <c r="G6" t="n">
         <v>89.86</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1244,7 +1249,6 @@
       <c r="G7" t="n">
         <v>89.86</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1301,7 +1305,6 @@
       <c r="G8" t="n">
         <v>89.86</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1358,7 +1361,6 @@
       <c r="G9" t="n">
         <v>169.17</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1415,7 +1417,6 @@
       <c r="G10" t="n">
         <v>179.49</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1472,7 +1473,6 @@
       <c r="G11" t="n">
         <v>134.06</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1529,7 +1529,6 @@
       <c r="G12" t="n">
         <v>161.28</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1586,7 +1585,6 @@
       <c r="G13" t="n">
         <v>161.28</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1643,7 +1641,6 @@
       <c r="G14" t="n">
         <v>161.28</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1700,7 +1697,6 @@
       <c r="G15" t="n">
         <v>161.28</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1757,7 +1753,6 @@
       <c r="G16" t="n">
         <v>89.86</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1814,7 +1809,6 @@
       <c r="G17" t="n">
         <v>169.17</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1871,7 +1865,6 @@
       <c r="G18" t="n">
         <v>179.49</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1928,7 +1921,6 @@
       <c r="G19" t="n">
         <v>161.12</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1985,7 +1977,6 @@
       <c r="G20" t="n">
         <v>134.06</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2042,7 +2033,6 @@
       <c r="G21" t="n">
         <v>119.41</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2099,7 +2089,6 @@
       <c r="G22" t="n">
         <v>167.77</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2156,7 +2145,6 @@
       <c r="G23" t="n">
         <v>161.28</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2213,7 +2201,6 @@
       <c r="G24" t="n">
         <v>119.41</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2270,7 +2257,6 @@
       <c r="G25" t="n">
         <v>161.28</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2327,7 +2313,6 @@
       <c r="G26" t="n">
         <v>119.41</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2384,7 +2369,6 @@
       <c r="G27" t="n">
         <v>161.28</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2441,7 +2425,6 @@
       <c r="G28" t="n">
         <v>119.41</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2498,7 +2481,6 @@
       <c r="G29" t="n">
         <v>119.41</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2555,7 +2537,6 @@
       <c r="G30" t="n">
         <v>161.28</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2612,7 +2593,6 @@
       <c r="G31" t="n">
         <v>89.86</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2669,7 +2649,6 @@
       <c r="G32" t="n">
         <v>89.86</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2726,7 +2705,6 @@
       <c r="G33" t="n">
         <v>194.3</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2783,7 +2761,6 @@
       <c r="G34" t="n">
         <v>194.3</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2840,7 +2817,6 @@
       <c r="G35" t="n">
         <v>194.3</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2897,7 +2873,6 @@
       <c r="G36" t="n">
         <v>194.2</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2954,7 +2929,6 @@
       <c r="G37" t="n">
         <v>194.2</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3011,7 +2985,6 @@
       <c r="G38" t="n">
         <v>194.2</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3068,7 +3041,6 @@
       <c r="G39" t="n">
         <v>194.2</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3125,7 +3097,6 @@
       <c r="G40" t="n">
         <v>194.2</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3182,7 +3153,6 @@
       <c r="G41" t="n">
         <v>194.2</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3239,7 +3209,6 @@
       <c r="G42" t="n">
         <v>194.2</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3296,7 +3265,6 @@
       <c r="G43" t="n">
         <v>194.3</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3353,7 +3321,6 @@
       <c r="G44" t="n">
         <v>194.3</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3410,7 +3377,6 @@
       <c r="G45" t="n">
         <v>376.65</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3467,7 +3433,6 @@
       <c r="G46" t="n">
         <v>376.65</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3524,7 +3489,6 @@
       <c r="G47" t="n">
         <v>383.83</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3581,7 +3545,6 @@
       <c r="G48" t="n">
         <v>383.83</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3638,7 +3601,6 @@
       <c r="G49" t="n">
         <v>383.83</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/palm-hills-alexandria.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-alexandria.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
